--- a/cds_files/ColoradoBoulder_CDS_2021-2022.xlsx
+++ b/cds_files/ColoradoBoulder_CDS_2021-2022.xlsx
@@ -434,7 +434,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32000</v>
+        <v>37956</v>
       </c>
     </row>
     <row r="5">
